--- a/employee_surveys/041_employee_wellness_questionnaire--employee_surveys.xlsx
+++ b/employee_surveys/041_employee_wellness_questionnaire--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'high_school',_'label':_'high_school_or_lower'}</t>
+          <t>high_school_or_lower</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'high_school', 'label': 'High School or Lower'}</t>
+          <t>High School or Lower</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'some_college',_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'some_college', 'label': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'bachelors',_'label':_'bachelors'}</t>
+          <t>bachelors</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'bachelors', 'label': 'Bachelors'}</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'masters',_'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'masters', 'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'non_manager',_'label':_'non-manager'}</t>
+          <t>non-manager</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'non_manager', 'label': 'Non-Manager'}</t>
+          <t>Non-Manager</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'marketing',_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'marketing', 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'sales',_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'sales', 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'finance',_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'finance', 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'entry_level',_'label':_'entry-level'}</t>
+          <t>entry-level</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'entry_level', 'label': 'Entry-Level'}</t>
+          <t>Entry-Level</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'mid_level',_'label':_'mid-level'}</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'mid_level', 'label': 'Mid-Level'}</t>
+          <t>Mid-Level</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'senior_level',_'label':_'senior-level'}</t>
+          <t>senior-level</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'senior_level', 'label': 'Senior-Level'}</t>
+          <t>Senior-Level</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'very_important',_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'very_important', 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'not_important',_'label':_'not_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'not_important', 'label': 'Not Important'}</t>
+          <t>Not Important</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied',_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'not_satisfied', 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'very_positive',_'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'very_positive', 'label': 'Very Positive'}</t>
+          <t>Very Positive</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_positive',_'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_positive', 'label': 'Somewhat Positive'}</t>
+          <t>Somewhat Positive</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'negative',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'negative', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
